--- a/student_data.xlsx
+++ b/student_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Panjunathan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Panjunathan\Desktop\student_data_visualization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{328168D8-D7A0-4976-AC66-27B166C0FD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499B882D-814F-4FCE-83C7-B7FFDD17A751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8D8CBE64-29D4-4FCD-BCBD-4A5EA7024203}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <t>Study_Hours</t>
   </si>
   <si>
-    <t>Attenance</t>
+    <t>Attendance</t>
   </si>
 </sst>
 </file>
@@ -393,6 +393,7 @@
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
